--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486270_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486270_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7971</v>
+        <v>3.2138</v>
       </c>
       <c r="E2" t="n">
-        <v>2.941</v>
+        <v>2.8777</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8561</v>
+        <v>0.3361</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.8617</v>
+        <v>1.7122</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.1319</v>
+        <v>-0.5262</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2701</v>
+        <v>2.2384</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.389</v>
+        <v>2.9053</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.4655</v>
+        <v>-0.1579</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0765</v>
+        <v>3.0632</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4727</v>
+        <v>-1.1931</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6663</v>
+        <v>-0.3683</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1936</v>
+        <v>-0.8248</v>
       </c>
       <c r="P2" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2689</v>
+        <v>-1.3886</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8977000000000001</v>
+        <v>-0.3076</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6287</v>
+        <v>-1.0809</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5199</v>
+        <v>2.4552</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5199</v>
+        <v>2.4552</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5934</v>
+        <v>2.9532</v>
       </c>
       <c r="E3" t="n">
-        <v>2.319</v>
+        <v>2.1587</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2744</v>
+        <v>0.7945</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7122</v>
+        <v>-1.8617</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5262</v>
+        <v>-2.1319</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2384</v>
+        <v>0.2701</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9053</v>
+        <v>-1.389</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1579</v>
+        <v>-1.4655</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0632</v>
+        <v>0.0765</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1931</v>
+        <v>-0.4727</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3683</v>
+        <v>-0.6663</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8248</v>
+        <v>0.1936</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6101</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.009</v>
+        <v>-0.575</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.1154</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1426</v>
+        <v>-0.6904</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4552</v>
+        <v>4.5199</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4552</v>
+        <v>4.5199</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5158</v>
+        <v>1.9384</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9244</v>
+        <v>2.6112</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4086</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3323</v>
+        <v>2.6444</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6446</v>
+        <v>1.1161</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3124</v>
+        <v>1.5284</v>
       </c>
       <c r="J4" t="n">
-        <v>1.335</v>
+        <v>3.4837</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6847</v>
+        <v>1.5329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6502</v>
+        <v>1.9507</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6672</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3293</v>
+        <v>-0.4169</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3379</v>
+        <v>-0.4224</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9557</v>
+        <v>-0.0111</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8292</v>
+        <v>0.2151</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1265</v>
+        <v>-0.2262</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4548</v>
+        <v>1.853</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2818</v>
+        <v>2.4773</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.827</v>
+        <v>-0.6244</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6444</v>
+        <v>-0.3323</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1161</v>
+        <v>-0.6446</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5284</v>
+        <v>0.3124</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4837</v>
+        <v>1.335</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5329</v>
+        <v>0.6847</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9507</v>
+        <v>0.6502</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-1.6672</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4169</v>
+        <v>-1.3293</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4224</v>
+        <v>-0.3379</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5053</v>
+        <v>0.2929</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8857</v>
+        <v>0.3822</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3803</v>
+        <v>-0.0892</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7147</v>
+        <v>0.969</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1483</v>
+        <v>1.3718</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4337</v>
+        <v>-0.4029</v>
       </c>
       <c r="G6" t="n">
         <v>1.3124</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8805</v>
+        <v>-1.6262</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9469</v>
+        <v>-0.7234</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9336</v>
+        <v>-0.9028</v>
       </c>
       <c r="V6" t="n">
         <v>0.1952</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.368</v>
+        <v>0.7862</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6584</v>
+        <v>1.6404</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2904</v>
+        <v>-0.8542</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.0088</v>
+        <v>-0.9771</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8971</v>
+        <v>0.6294</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1117</v>
+        <v>-1.6065</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1566</v>
+        <v>1.0416</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.08169999999999999</v>
+        <v>1.8432</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.8016</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8521</v>
+        <v>-2.0187</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8153</v>
+        <v>-1.2138</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0368</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4487</v>
+        <v>-1.5418</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2704</v>
+        <v>-0.5311</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1783</v>
+        <v>-1.0106</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0854</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>2.0854</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2043</v>
+        <v>0.2447</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3051</v>
+        <v>1.6584</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1008</v>
+        <v>-1.4137</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9771</v>
+        <v>-3.0088</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6294</v>
+        <v>-0.8971</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6065</v>
+        <v>-2.1117</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0416</v>
+        <v>-0.1566</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8432</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8016</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0187</v>
+        <v>-2.8521</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2138</v>
+        <v>-0.8153</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-2.0368</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1236</v>
+        <v>-0.572</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.2704</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2572</v>
+        <v>-0.3016</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>2.0854</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>2.0854</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1254</v>
+        <v>0.2256</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2341</v>
+        <v>-0.0105</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3594</v>
+        <v>0.2361</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2719</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6903</v>
+        <v>-0.59</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4675</v>
+        <v>-0.2439</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2228</v>
+        <v>-0.3461</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.819</v>
+        <v>-1.6764</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6586</v>
+        <v>-0.5468</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1604</v>
+        <v>-1.1296</v>
       </c>
       <c r="G10" t="n">
         <v>-1.485</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.334</v>
+        <v>-0.1914</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2055</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1443</v>
+        <v>-2.7358</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.864</v>
+        <v>-2.6405</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2803</v>
+        <v>-0.0953</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0703</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7912</v>
+        <v>-0.3827</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.536</v>
+        <v>-0.3124</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2552</v>
+        <v>-0.0703</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4471</v>
+        <v>-5.4086</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.285</v>
+        <v>-4.0615</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1622</v>
+        <v>-1.3471</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3118</v>
@@ -1390,13 +1390,13 @@
         <v>2.6101</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0053</v>
+        <v>-0.9668</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5323</v>
+        <v>-0.3088</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.473</v>
+        <v>-0.6579</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5649999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3631</v>
+        <v>2.363100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>7.536300000000001</v>
+        <v>7.536200000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.173500000000001</v>
+        <v>-5.1734</v>
       </c>
       <c r="G13" t="n">
         <v>-7.649899999999999</v>
@@ -1441,7 +1441,7 @@
         <v>-5.4147</v>
       </c>
       <c r="J13" t="n">
-        <v>8.062100000000001</v>
+        <v>8.062099999999999</v>
       </c>
       <c r="K13" t="n">
         <v>4.260699999999999</v>
@@ -1471,10 +1471,10 @@
         <v>-7.5527</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.078799999999999</v>
+        <v>-2.0786</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.4737</v>
+        <v>-5.473599999999999</v>
       </c>
       <c r="V13" t="n">
         <v>8.8653</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.442</v>
+        <v>8.8146</v>
       </c>
       <c r="E14" t="n">
-        <v>8.4137</v>
+        <v>8.6372</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0283</v>
+        <v>0.1773</v>
       </c>
       <c r="G14" t="n">
         <v>9.148999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0755</v>
+        <v>1.448</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5997</v>
+        <v>0.8232</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4759</v>
+        <v>0.6249</v>
       </c>
       <c r="V14" t="n">
         <v>-1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2916</v>
+        <v>1.9141</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4272</v>
+        <v>0.5273</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8645</v>
+        <v>1.3868</v>
       </c>
       <c r="G15" t="n">
         <v>1.0651</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5316</v>
+        <v>2.154</v>
       </c>
       <c r="T15" t="n">
-        <v>3.0643</v>
+        <v>1.1645</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4672</v>
+        <v>0.9896</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2213</v>
+        <v>1.2406</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4991</v>
+        <v>0.6109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7222</v>
+        <v>0.6297</v>
       </c>
       <c r="G16" t="n">
         <v>0.3613</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5104</v>
+        <v>0.5296</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0961</v>
+        <v>0.2079</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4142</v>
+        <v>0.3217</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9554</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8569</v>
+        <v>0.7014</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8776</v>
+        <v>2.5424</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0208</v>
+        <v>-1.8409</v>
       </c>
       <c r="G17" t="n">
         <v>3.4128</v>
@@ -1780,13 +1780,13 @@
         <v>0.435</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0961</v>
+        <v>0.9406</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6886</v>
+        <v>0.3533</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4075</v>
+        <v>0.5873</v>
       </c>
       <c r="V17" t="n">
         <v>-2.9995</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.43</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8212</v>
+        <v>1.4917</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2512</v>
+        <v>-0.8864</v>
       </c>
       <c r="G18" t="n">
         <v>1.3234</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2107</v>
+        <v>0.8247</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0481</v>
+        <v>0.7186</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2587</v>
+        <v>0.106</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3252</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4639</v>
+        <v>0.4404</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4307</v>
+        <v>0.0164</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0332</v>
+        <v>0.424</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4759</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6405</v>
+        <v>0.2638</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.2944</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1009</v>
+        <v>0.5582</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8482</v>
+        <v>-0.1597</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0444</v>
+        <v>0.4026</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8038</v>
+        <v>-0.5623</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3943</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2364</v>
+        <v>0.4521</v>
       </c>
       <c r="T20" t="n">
-        <v>0.149</v>
+        <v>0.596</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3854</v>
+        <v>-0.1439</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7077</v>
+        <v>-1.3312</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3656</v>
+        <v>-0.0162</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3421</v>
+        <v>-1.3149</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.492</v>
+        <v>-0.5506</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2858</v>
+        <v>0.432</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7778</v>
+        <v>-0.9825</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7731</v>
+        <v>0.0042</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6022</v>
+        <v>0.8823</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3754</v>
+        <v>-0.8781</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7188</v>
+        <v>-0.5548</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3164</v>
+        <v>-0.4504</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4024</v>
+        <v>-0.1044</v>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.2175</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.0875</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0018</v>
+        <v>0.3494</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4951</v>
+        <v>0.1971</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4933</v>
+        <v>0.1523</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7833</v>
+        <v>-1.8516</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0162</v>
+        <v>-1.8126</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7671</v>
+        <v>-0.039</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5506</v>
+        <v>-1.492</v>
       </c>
       <c r="H22" t="n">
-        <v>0.432</v>
+        <v>0.2858</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9825</v>
+        <v>-1.7778</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0042</v>
+        <v>-0.7731</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8823</v>
+        <v>0.6022</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8781</v>
+        <v>-1.3754</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5548</v>
+        <v>-0.7188</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4504</v>
+        <v>-0.3164</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1044</v>
+        <v>-0.4024</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1027</v>
+        <v>-0.1421</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1971</v>
+        <v>0.0481</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2998</v>
+        <v>-0.1902</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>L. TERRY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3628</v>
+        <v>-2.4391</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8766</v>
+        <v>-2.955</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4862</v>
+        <v>0.5159</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.296</v>
+        <v>0.0278</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.7183</v>
+        <v>0.9944</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5777</v>
+        <v>-0.9666</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3971</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4354</v>
+        <v>1.4631</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0382</v>
+        <v>-1.3737</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8989</v>
+        <v>-0.0616</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2829</v>
+        <v>-0.4688</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.616</v>
+        <v>0.4072</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.305</v>
+        <v>-4.1326</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.305</v>
+        <v>-5.6552</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.296</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8256</v>
+        <v>0.3509</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1729</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7602</v>
+        <v>0.3698</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7602</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. TERRY</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6786</v>
+        <v>-3.2446</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7373</v>
+        <v>-1.8766</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0587</v>
+        <v>-1.368</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0278</v>
+        <v>-2.296</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9944</v>
+        <v>-1.7183</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9666</v>
+        <v>-0.5777</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08939999999999999</v>
+        <v>-1.3971</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4631</v>
+        <v>-1.4354</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3737</v>
+        <v>0.0382</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0616</v>
+        <v>-0.8989</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4688</v>
+        <v>-0.2829</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4072</v>
+        <v>-0.616</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.1326</v>
+        <v>-1.305</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.6552</v>
+        <v>-1.305</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0565</v>
+        <v>1.1167</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4314</v>
+        <v>0.8256</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4879</v>
+        <v>0.2911</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3698</v>
+        <v>-0.7602</v>
       </c>
       <c r="W24" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.8902</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9004</v>
+        <v>-4.8182</v>
       </c>
       <c r="E25" t="n">
         <v>-2.3947</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5057</v>
+        <v>-2.4234</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4807</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4726</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>0.4831</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0105</v>
+        <v>0.0718</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9347</v>
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.363100000000002</v>
+        <v>-0.1279999999999992</v>
       </c>
       <c r="E26" t="n">
-        <v>5.173300000000001</v>
+        <v>5.173400000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.5364</v>
+        <v>-5.3012</v>
       </c>
       <c r="G26" t="n">
-        <v>7.649899999999999</v>
+        <v>7.649899999999997</v>
       </c>
       <c r="H26" t="n">
         <v>2.2353</v>
       </c>
       <c r="I26" t="n">
-        <v>5.414800000000001</v>
+        <v>5.4148</v>
       </c>
       <c r="J26" t="n">
         <v>15.7118</v>
       </c>
       <c r="K26" t="n">
-        <v>6.4958</v>
+        <v>6.495799999999999</v>
       </c>
       <c r="L26" t="n">
         <v>9.2159</v>
@@ -2473,25 +2473,25 @@
         <v>-3.8012</v>
       </c>
       <c r="P26" t="n">
-        <v>-8.700200000000001</v>
+        <v>-8.700199999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-18.488</v>
       </c>
       <c r="R26" t="n">
-        <v>9.787600000000001</v>
+        <v>9.787599999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>7.5527</v>
+        <v>9.787699999999999</v>
       </c>
       <c r="T26" t="n">
         <v>5.4739</v>
       </c>
       <c r="U26" t="n">
-        <v>2.0788</v>
+        <v>4.3139</v>
       </c>
       <c r="V26" t="n">
-        <v>-8.865199999999998</v>
+        <v>-8.8652</v>
       </c>
       <c r="W26" t="n">
         <v>2.4758</v>
